--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-05-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-05-2025.xlsx
@@ -134,6 +134,111 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £13.33</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £16.99</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £18.22</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £23.11</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £24.68</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £28.97</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £30.99</t>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £37.57</t>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £47.29</t>
+      </text>
+    </comment>
+    <comment ref="H16" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.14</t>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £33.99</t>
+      </text>
+    </comment>
+    <comment ref="H20" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £43.99</t>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £46.50</t>
+      </text>
+    </comment>
+    <comment ref="H22" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £55.11</t>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £50.30</t>
+      </text>
+    </comment>
+    <comment ref="H26" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £48.04</t>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £1319.68</t>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £1458.4</t>
+      </text>
+    </comment>
+    <comment ref="H29" authorId="0" shapeId="0">
+      <text>
+        <t>Previous Price: £1424.16</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3243,5 +3348,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>